--- a/source/_static/report/TRJ3_sample_r51.xlsx
+++ b/source/_static/report/TRJ3_sample_r51.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\office\counter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\siq\github\cop5\source\_static\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D3FD0C6-3CA0-4012-A776-0D5FD8C9523C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB89F63-3BE0-4FA7-A649-5CC2168D1020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TRJ3_sample_r51" sheetId="1" r:id="rId1"/>
@@ -57,9 +57,6 @@
     <t>Institution_ID</t>
   </si>
   <si>
-    <t>ISNI:1234123412341234</t>
-  </si>
-  <si>
     <t>Metric_Types</t>
   </si>
   <si>
@@ -211,6 +208,9 @@
   </si>
   <si>
     <t>Open</t>
+  </si>
+  <si>
+    <t>P1:1234; ISNI:1234123412341234</t>
   </si>
 </sst>
 </file>
@@ -249,12 +249,12 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -380,7 +380,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5703125" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.7109375" style="1" customWidth="1"/>
@@ -444,171 +444,171 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="J15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="K15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="L15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="M15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="M15" s="1" t="s">
+      <c r="N15" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="N15" s="1" t="s">
+      <c r="O15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="O15" s="1" t="s">
+      <c r="P15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="P15" s="1" t="s">
+      <c r="Q15" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="Q15" s="1" t="s">
+      <c r="R15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="R15" s="1" t="s">
+      <c r="S15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="S15" s="1" t="s">
+      <c r="T15" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="T15" s="1" t="s">
+      <c r="U15" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="U15" s="1" t="s">
+      <c r="V15" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="V15" s="1" t="s">
+      <c r="W15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="W15" s="1" t="s">
+      <c r="X15" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="X15" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="J16" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="K16" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="L16" s="2">
         <v>9110</v>
@@ -652,34 +652,34 @@
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="K17" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L17" s="2">
         <v>5736</v>
@@ -723,34 +723,34 @@
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="J18" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="K18" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L18" s="2">
         <v>7004</v>
@@ -794,34 +794,34 @@
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="H19" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="I19" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="J19" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="K19" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L19" s="2">
         <v>4476</v>
@@ -865,34 +865,34 @@
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="E20" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="H20" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="I20" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I20" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="J20" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L20" s="2">
         <v>26012</v>
@@ -936,34 +936,34 @@
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="H21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I21" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="J21" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L21" s="2">
         <v>15902</v>
@@ -1007,34 +1007,34 @@
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I22" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="J22" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L22" s="2">
         <v>19692</v>
@@ -1078,34 +1078,34 @@
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="H23" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I23" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="J23" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L23" s="2">
         <v>12110</v>
